--- a/Survey_data_real.xlsx
+++ b/Survey_data_real.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop (1)\Other\ShinyAPPnorway\ACCESS-FjordAPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B8E29A-375B-47D9-AFB9-1A8952A2FA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1872787-23C7-4B9E-9A76-5C5ABB3E7755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="149">
   <si>
     <t>Date</t>
   </si>
@@ -457,6 +457,33 @@
   </si>
   <si>
     <t>Crab munida rugosa</t>
+  </si>
+  <si>
+    <t>Bait fish</t>
+  </si>
+  <si>
+    <t>Kalovika opposite deep</t>
+  </si>
+  <si>
+    <t>lovefish</t>
+  </si>
+  <si>
+    <t>Redfish</t>
+  </si>
+  <si>
+    <t>lost halibut metal jig</t>
+  </si>
+  <si>
+    <t>Renato</t>
+  </si>
+  <si>
+    <t>Jack</t>
+  </si>
+  <si>
+    <t>Marco2</t>
+  </si>
+  <si>
+    <t>Pino</t>
   </si>
 </sst>
 </file>
@@ -835,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J180"/>
+  <dimension ref="A1:J229"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.7265625" style="2" customWidth="1"/>
@@ -5068,6 +5095,1169 @@
       </c>
       <c r="H180" t="s">
         <v>119</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A181" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B181" t="s">
+        <v>110</v>
+      </c>
+      <c r="C181" t="s">
+        <v>142</v>
+      </c>
+      <c r="D181" t="s">
+        <v>40</v>
+      </c>
+      <c r="E181" t="s">
+        <v>6</v>
+      </c>
+      <c r="F181">
+        <v>52</v>
+      </c>
+      <c r="G181">
+        <v>1435</v>
+      </c>
+      <c r="I181" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A182" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B182" t="s">
+        <v>110</v>
+      </c>
+      <c r="C182" t="s">
+        <v>142</v>
+      </c>
+      <c r="D182" t="s">
+        <v>40</v>
+      </c>
+      <c r="E182" t="s">
+        <v>6</v>
+      </c>
+      <c r="F182">
+        <v>55</v>
+      </c>
+      <c r="G182">
+        <v>1665</v>
+      </c>
+      <c r="I182" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A183" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B183" t="s">
+        <v>110</v>
+      </c>
+      <c r="C183" t="s">
+        <v>86</v>
+      </c>
+      <c r="D183" t="s">
+        <v>40</v>
+      </c>
+      <c r="E183" t="s">
+        <v>6</v>
+      </c>
+      <c r="F183">
+        <v>45</v>
+      </c>
+      <c r="G183">
+        <v>750</v>
+      </c>
+      <c r="I183" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A184" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B184" t="s">
+        <v>123</v>
+      </c>
+      <c r="D184" t="s">
+        <v>40</v>
+      </c>
+      <c r="E184" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A185" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B185" t="s">
+        <v>54</v>
+      </c>
+      <c r="C185" t="s">
+        <v>142</v>
+      </c>
+      <c r="D185" t="s">
+        <v>40</v>
+      </c>
+      <c r="E185" t="s">
+        <v>103</v>
+      </c>
+      <c r="F185">
+        <v>32</v>
+      </c>
+      <c r="G185">
+        <v>285</v>
+      </c>
+      <c r="H185" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A186" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B186" t="s">
+        <v>54</v>
+      </c>
+      <c r="C186" t="s">
+        <v>86</v>
+      </c>
+      <c r="D186" t="s">
+        <v>40</v>
+      </c>
+      <c r="E186" t="s">
+        <v>103</v>
+      </c>
+      <c r="F186">
+        <v>33</v>
+      </c>
+      <c r="G186">
+        <v>290</v>
+      </c>
+      <c r="H186" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A187" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B187" t="s">
+        <v>54</v>
+      </c>
+      <c r="C187" t="s">
+        <v>142</v>
+      </c>
+      <c r="D187" t="s">
+        <v>96</v>
+      </c>
+      <c r="E187" t="s">
+        <v>68</v>
+      </c>
+      <c r="F187">
+        <v>79</v>
+      </c>
+      <c r="G187">
+        <v>5380</v>
+      </c>
+      <c r="I187" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A188" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B188" t="s">
+        <v>54</v>
+      </c>
+      <c r="C188" t="s">
+        <v>142</v>
+      </c>
+      <c r="D188" t="s">
+        <v>40</v>
+      </c>
+      <c r="E188" t="s">
+        <v>103</v>
+      </c>
+      <c r="F188">
+        <v>31</v>
+      </c>
+      <c r="G188">
+        <v>265</v>
+      </c>
+      <c r="H188" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A189" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B189" t="s">
+        <v>54</v>
+      </c>
+      <c r="C189" t="s">
+        <v>142</v>
+      </c>
+      <c r="D189" t="s">
+        <v>40</v>
+      </c>
+      <c r="E189" t="s">
+        <v>83</v>
+      </c>
+      <c r="F189">
+        <v>39</v>
+      </c>
+      <c r="G189">
+        <v>480</v>
+      </c>
+      <c r="H189" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A190" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B190" t="s">
+        <v>54</v>
+      </c>
+      <c r="C190" t="s">
+        <v>142</v>
+      </c>
+      <c r="D190" t="s">
+        <v>40</v>
+      </c>
+      <c r="E190" t="s">
+        <v>83</v>
+      </c>
+      <c r="F190">
+        <v>33</v>
+      </c>
+      <c r="G190">
+        <v>340</v>
+      </c>
+      <c r="H190" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A191" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B191" t="s">
+        <v>54</v>
+      </c>
+      <c r="C191" t="s">
+        <v>142</v>
+      </c>
+      <c r="D191" t="s">
+        <v>40</v>
+      </c>
+      <c r="E191" t="s">
+        <v>83</v>
+      </c>
+      <c r="F191">
+        <v>63</v>
+      </c>
+      <c r="G191">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A192" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B192" t="s">
+        <v>44</v>
+      </c>
+      <c r="C192" t="s">
+        <v>142</v>
+      </c>
+      <c r="D192" t="s">
+        <v>40</v>
+      </c>
+      <c r="E192" t="s">
+        <v>143</v>
+      </c>
+      <c r="F192">
+        <v>27</v>
+      </c>
+      <c r="G192">
+        <v>225</v>
+      </c>
+      <c r="H192" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A193" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B193" t="s">
+        <v>44</v>
+      </c>
+      <c r="C193" t="s">
+        <v>86</v>
+      </c>
+      <c r="D193" t="s">
+        <v>40</v>
+      </c>
+      <c r="E193" t="s">
+        <v>83</v>
+      </c>
+      <c r="F193">
+        <v>49</v>
+      </c>
+      <c r="G193">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A194" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B194" t="s">
+        <v>44</v>
+      </c>
+      <c r="C194" t="s">
+        <v>86</v>
+      </c>
+      <c r="D194" t="s">
+        <v>40</v>
+      </c>
+      <c r="E194" t="s">
+        <v>83</v>
+      </c>
+      <c r="F194">
+        <v>48</v>
+      </c>
+      <c r="G194">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A195" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B195" t="s">
+        <v>44</v>
+      </c>
+      <c r="C195" t="s">
+        <v>142</v>
+      </c>
+      <c r="D195" t="s">
+        <v>40</v>
+      </c>
+      <c r="E195" t="s">
+        <v>6</v>
+      </c>
+      <c r="F195">
+        <v>51</v>
+      </c>
+      <c r="G195">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A196" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B196" t="s">
+        <v>44</v>
+      </c>
+      <c r="C196" t="s">
+        <v>142</v>
+      </c>
+      <c r="D196" t="s">
+        <v>40</v>
+      </c>
+      <c r="E196" t="s">
+        <v>103</v>
+      </c>
+      <c r="F196">
+        <v>42</v>
+      </c>
+      <c r="G196">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A197" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B197" t="s">
+        <v>54</v>
+      </c>
+      <c r="C197" t="s">
+        <v>86</v>
+      </c>
+      <c r="D197" t="s">
+        <v>60</v>
+      </c>
+      <c r="E197" t="s">
+        <v>137</v>
+      </c>
+      <c r="F197">
+        <v>43</v>
+      </c>
+      <c r="G197">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A198" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B198" t="s">
+        <v>141</v>
+      </c>
+      <c r="C198" t="s">
+        <v>86</v>
+      </c>
+      <c r="D198" t="s">
+        <v>60</v>
+      </c>
+      <c r="E198" t="s">
+        <v>143</v>
+      </c>
+      <c r="F198">
+        <v>48</v>
+      </c>
+      <c r="G198">
+        <v>1300</v>
+      </c>
+      <c r="H198" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A199" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B199" t="s">
+        <v>141</v>
+      </c>
+      <c r="C199" t="s">
+        <v>142</v>
+      </c>
+      <c r="D199" t="s">
+        <v>60</v>
+      </c>
+      <c r="E199" t="s">
+        <v>6</v>
+      </c>
+      <c r="F199">
+        <v>85</v>
+      </c>
+      <c r="G199">
+        <v>4495</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A200" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B200" t="s">
+        <v>141</v>
+      </c>
+      <c r="C200" t="s">
+        <v>142</v>
+      </c>
+      <c r="D200" t="s">
+        <v>60</v>
+      </c>
+      <c r="E200" t="s">
+        <v>83</v>
+      </c>
+      <c r="F200">
+        <v>50</v>
+      </c>
+      <c r="G200">
+        <v>900</v>
+      </c>
+      <c r="H200" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A201" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B201" t="s">
+        <v>141</v>
+      </c>
+      <c r="C201" t="s">
+        <v>86</v>
+      </c>
+      <c r="D201" t="s">
+        <v>60</v>
+      </c>
+      <c r="E201" t="s">
+        <v>83</v>
+      </c>
+      <c r="F201">
+        <v>56</v>
+      </c>
+      <c r="G201">
+        <v>1350</v>
+      </c>
+      <c r="H201" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A202" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B202" t="s">
+        <v>44</v>
+      </c>
+      <c r="C202" t="s">
+        <v>142</v>
+      </c>
+      <c r="D202" t="s">
+        <v>40</v>
+      </c>
+      <c r="E202" t="s">
+        <v>103</v>
+      </c>
+      <c r="F202">
+        <v>41</v>
+      </c>
+      <c r="G202">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A203" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B203" t="s">
+        <v>44</v>
+      </c>
+      <c r="C203" t="s">
+        <v>142</v>
+      </c>
+      <c r="D203" t="s">
+        <v>40</v>
+      </c>
+      <c r="E203" t="s">
+        <v>103</v>
+      </c>
+      <c r="F203">
+        <v>41</v>
+      </c>
+      <c r="G203">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A204" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B204" t="s">
+        <v>44</v>
+      </c>
+      <c r="C204" t="s">
+        <v>147</v>
+      </c>
+      <c r="D204" t="s">
+        <v>40</v>
+      </c>
+      <c r="E204" t="s">
+        <v>83</v>
+      </c>
+      <c r="F204">
+        <v>41</v>
+      </c>
+      <c r="G204">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A205" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B205" t="s">
+        <v>44</v>
+      </c>
+      <c r="C205" t="s">
+        <v>147</v>
+      </c>
+      <c r="D205" t="s">
+        <v>40</v>
+      </c>
+      <c r="E205" t="s">
+        <v>83</v>
+      </c>
+      <c r="F205">
+        <v>33</v>
+      </c>
+      <c r="G205">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A206" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B206" t="s">
+        <v>44</v>
+      </c>
+      <c r="C206" t="s">
+        <v>142</v>
+      </c>
+      <c r="D206" t="s">
+        <v>40</v>
+      </c>
+      <c r="E206" t="s">
+        <v>83</v>
+      </c>
+      <c r="F206">
+        <v>32</v>
+      </c>
+      <c r="G206">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A207" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B207" t="s">
+        <v>44</v>
+      </c>
+      <c r="C207" t="s">
+        <v>146</v>
+      </c>
+      <c r="D207" t="s">
+        <v>40</v>
+      </c>
+      <c r="E207" t="s">
+        <v>83</v>
+      </c>
+      <c r="F207">
+        <v>50</v>
+      </c>
+      <c r="G207">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A208" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B208" t="s">
+        <v>44</v>
+      </c>
+      <c r="C208" t="s">
+        <v>148</v>
+      </c>
+      <c r="D208" t="s">
+        <v>40</v>
+      </c>
+      <c r="E208" t="s">
+        <v>143</v>
+      </c>
+      <c r="F208">
+        <v>26</v>
+      </c>
+      <c r="G208">
+        <v>200</v>
+      </c>
+      <c r="I208" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A209" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B209" t="s">
+        <v>44</v>
+      </c>
+      <c r="C209" t="s">
+        <v>145</v>
+      </c>
+      <c r="D209" t="s">
+        <v>40</v>
+      </c>
+      <c r="E209" t="s">
+        <v>83</v>
+      </c>
+      <c r="F209">
+        <v>50</v>
+      </c>
+      <c r="I209" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A210" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B210" t="s">
+        <v>44</v>
+      </c>
+      <c r="C210" t="s">
+        <v>147</v>
+      </c>
+      <c r="D210" t="s">
+        <v>40</v>
+      </c>
+      <c r="E210" t="s">
+        <v>83</v>
+      </c>
+      <c r="F210">
+        <v>48</v>
+      </c>
+      <c r="I210" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A211" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B211" t="s">
+        <v>44</v>
+      </c>
+      <c r="C211" t="s">
+        <v>147</v>
+      </c>
+      <c r="D211" t="s">
+        <v>40</v>
+      </c>
+      <c r="E211" t="s">
+        <v>83</v>
+      </c>
+      <c r="F211">
+        <v>44</v>
+      </c>
+      <c r="I211" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A212" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B212" t="s">
+        <v>44</v>
+      </c>
+      <c r="C212" t="s">
+        <v>148</v>
+      </c>
+      <c r="D212" t="s">
+        <v>40</v>
+      </c>
+      <c r="E212" t="s">
+        <v>83</v>
+      </c>
+      <c r="F212">
+        <v>35</v>
+      </c>
+      <c r="I212" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A213" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B213" t="s">
+        <v>112</v>
+      </c>
+      <c r="C213" t="s">
+        <v>142</v>
+      </c>
+      <c r="D213" t="s">
+        <v>40</v>
+      </c>
+      <c r="E213" t="s">
+        <v>83</v>
+      </c>
+      <c r="F213">
+        <v>32</v>
+      </c>
+      <c r="I213" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A214" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B214" t="s">
+        <v>112</v>
+      </c>
+      <c r="C214" t="s">
+        <v>142</v>
+      </c>
+      <c r="D214" t="s">
+        <v>40</v>
+      </c>
+      <c r="E214" t="s">
+        <v>103</v>
+      </c>
+      <c r="F214">
+        <v>35</v>
+      </c>
+      <c r="I214" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A215" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B215" t="s">
+        <v>112</v>
+      </c>
+      <c r="C215" t="s">
+        <v>145</v>
+      </c>
+      <c r="D215" t="s">
+        <v>60</v>
+      </c>
+      <c r="E215" t="s">
+        <v>52</v>
+      </c>
+      <c r="F215">
+        <v>49</v>
+      </c>
+      <c r="G215">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A216" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B216" t="s">
+        <v>112</v>
+      </c>
+      <c r="C216" t="s">
+        <v>147</v>
+      </c>
+      <c r="D216" t="s">
+        <v>60</v>
+      </c>
+      <c r="E216" t="s">
+        <v>6</v>
+      </c>
+      <c r="F216">
+        <v>68</v>
+      </c>
+      <c r="G216">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A217" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B217" t="s">
+        <v>112</v>
+      </c>
+      <c r="C217" t="s">
+        <v>146</v>
+      </c>
+      <c r="D217" t="s">
+        <v>41</v>
+      </c>
+      <c r="E217" t="s">
+        <v>6</v>
+      </c>
+      <c r="F217">
+        <v>50</v>
+      </c>
+      <c r="G217">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A218" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B218" t="s">
+        <v>112</v>
+      </c>
+      <c r="C218" t="s">
+        <v>148</v>
+      </c>
+      <c r="D218" t="s">
+        <v>60</v>
+      </c>
+      <c r="E218" t="s">
+        <v>61</v>
+      </c>
+      <c r="F218">
+        <v>60</v>
+      </c>
+      <c r="G218">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A219" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B219" t="s">
+        <v>112</v>
+      </c>
+      <c r="C219" t="s">
+        <v>145</v>
+      </c>
+      <c r="D219" t="s">
+        <v>41</v>
+      </c>
+      <c r="E219" t="s">
+        <v>61</v>
+      </c>
+      <c r="F219">
+        <v>49</v>
+      </c>
+      <c r="G219">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A220" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B220" t="s">
+        <v>44</v>
+      </c>
+      <c r="C220" t="s">
+        <v>146</v>
+      </c>
+      <c r="D220" t="s">
+        <v>40</v>
+      </c>
+      <c r="E220" t="s">
+        <v>6</v>
+      </c>
+      <c r="F220">
+        <v>69</v>
+      </c>
+      <c r="G220">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A221" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B221" t="s">
+        <v>44</v>
+      </c>
+      <c r="C221" t="s">
+        <v>142</v>
+      </c>
+      <c r="D221" t="s">
+        <v>40</v>
+      </c>
+      <c r="E221" t="s">
+        <v>6</v>
+      </c>
+      <c r="F221">
+        <v>63</v>
+      </c>
+      <c r="G221">
+        <v>2080</v>
+      </c>
+      <c r="H221" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A222" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B222" t="s">
+        <v>44</v>
+      </c>
+      <c r="C222" t="s">
+        <v>146</v>
+      </c>
+      <c r="D222" t="s">
+        <v>40</v>
+      </c>
+      <c r="E222" t="s">
+        <v>6</v>
+      </c>
+      <c r="F222">
+        <v>55</v>
+      </c>
+      <c r="I222" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A223" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B223" t="s">
+        <v>44</v>
+      </c>
+      <c r="C223" t="s">
+        <v>145</v>
+      </c>
+      <c r="D223" t="s">
+        <v>96</v>
+      </c>
+      <c r="E223" t="s">
+        <v>68</v>
+      </c>
+      <c r="F223">
+        <v>109</v>
+      </c>
+      <c r="G223">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A224" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B224" t="s">
+        <v>42</v>
+      </c>
+      <c r="C224" t="s">
+        <v>142</v>
+      </c>
+      <c r="D224" t="s">
+        <v>96</v>
+      </c>
+      <c r="E224" t="s">
+        <v>6</v>
+      </c>
+      <c r="F224">
+        <v>113</v>
+      </c>
+      <c r="G224">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A225" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B225" t="s">
+        <v>42</v>
+      </c>
+      <c r="C225" t="s">
+        <v>147</v>
+      </c>
+      <c r="D225" t="s">
+        <v>40</v>
+      </c>
+      <c r="E225" t="s">
+        <v>103</v>
+      </c>
+      <c r="F225">
+        <v>40</v>
+      </c>
+      <c r="I225" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A226" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B226" t="s">
+        <v>42</v>
+      </c>
+      <c r="C226" t="s">
+        <v>142</v>
+      </c>
+      <c r="D226" t="s">
+        <v>40</v>
+      </c>
+      <c r="E226" t="s">
+        <v>103</v>
+      </c>
+      <c r="F226">
+        <v>42</v>
+      </c>
+      <c r="I226" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A227" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B227" t="s">
+        <v>42</v>
+      </c>
+      <c r="C227" t="s">
+        <v>147</v>
+      </c>
+      <c r="D227" t="s">
+        <v>40</v>
+      </c>
+      <c r="E227" t="s">
+        <v>103</v>
+      </c>
+      <c r="F227">
+        <v>31</v>
+      </c>
+      <c r="I227" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A228" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B228" t="s">
+        <v>42</v>
+      </c>
+      <c r="C228" t="s">
+        <v>147</v>
+      </c>
+      <c r="D228" t="s">
+        <v>40</v>
+      </c>
+      <c r="E228" t="s">
+        <v>103</v>
+      </c>
+      <c r="F228">
+        <v>33</v>
+      </c>
+      <c r="I228" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A229" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B229" t="s">
+        <v>42</v>
+      </c>
+      <c r="C229" t="s">
+        <v>142</v>
+      </c>
+      <c r="D229" t="s">
+        <v>40</v>
+      </c>
+      <c r="E229" t="s">
+        <v>103</v>
+      </c>
+      <c r="F229">
+        <v>30</v>
+      </c>
+      <c r="I229" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -7608,6 +8798,12 @@
       <c r="J48" s="6">
         <v>3</v>
       </c>
+      <c r="K48" s="6">
+        <v>25</v>
+      </c>
+      <c r="L48" s="6">
+        <v>70</v>
+      </c>
       <c r="O48" t="s">
         <v>55</v>
       </c>
@@ -7843,54 +9039,495 @@
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C53" s="4"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
+      <c r="A53" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="2">
+        <v>46267</v>
+      </c>
+      <c r="D53" s="3">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F53" s="6">
+        <v>67.516900000000007</v>
+      </c>
+      <c r="G53" s="6">
+        <v>15.5364</v>
+      </c>
+      <c r="H53" s="6">
+        <v>67.516900000000007</v>
+      </c>
+      <c r="I53" s="6">
+        <v>15.5364</v>
+      </c>
+      <c r="J53" s="6">
+        <v>2</v>
+      </c>
+      <c r="K53" s="6">
+        <v>12</v>
+      </c>
+      <c r="L53" s="6">
+        <v>40</v>
+      </c>
+      <c r="M53" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="N53" s="6">
+        <v>27</v>
+      </c>
+      <c r="O53" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>38</v>
+      </c>
+      <c r="R53" t="s">
+        <v>56</v>
+      </c>
+      <c r="T53" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C54" s="4"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
+      <c r="A54" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="2">
+        <v>46267</v>
+      </c>
+      <c r="D54" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="E54" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="F54" s="6">
+        <v>67.550299999999993</v>
+      </c>
+      <c r="G54" s="6">
+        <v>15.625999999999999</v>
+      </c>
+      <c r="H54" s="6">
+        <v>67.550299999999993</v>
+      </c>
+      <c r="I54" s="6">
+        <v>15.625999999999999</v>
+      </c>
+      <c r="J54" s="6">
+        <v>2</v>
+      </c>
+      <c r="K54" s="6">
+        <v>25</v>
+      </c>
+      <c r="L54" s="6">
+        <v>80</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>38</v>
+      </c>
+      <c r="R54" t="s">
+        <v>56</v>
+      </c>
+      <c r="T54" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C55" s="4"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="2">
+        <v>46267</v>
+      </c>
+      <c r="D55" s="3">
+        <v>0.44027777777777777</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="F55" s="6">
+        <v>67.5792</v>
+      </c>
+      <c r="G55" s="6">
+        <v>15.7844</v>
+      </c>
+      <c r="H55" s="7">
+        <v>67.5792</v>
+      </c>
+      <c r="I55" s="6">
+        <v>15.7844</v>
+      </c>
+      <c r="J55" s="6">
+        <v>2</v>
+      </c>
+      <c r="K55" s="6">
+        <v>10</v>
+      </c>
+      <c r="L55" s="6">
+        <v>50</v>
+      </c>
+      <c r="M55" s="6">
+        <v>13.1</v>
+      </c>
+      <c r="N55" s="6">
+        <v>27.4</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>38</v>
+      </c>
+      <c r="R55" t="s">
+        <v>56</v>
+      </c>
+      <c r="S55" t="s">
+        <v>144</v>
+      </c>
+      <c r="T55" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C56" s="4"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
+      <c r="A56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2">
+        <v>46267</v>
+      </c>
+      <c r="D56" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0.8125</v>
+      </c>
+      <c r="F56" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="G56" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="H56" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="I56" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="J56" s="6">
+        <v>2</v>
+      </c>
+      <c r="K56" s="6">
+        <v>30</v>
+      </c>
+      <c r="L56" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>38</v>
+      </c>
+      <c r="R56" t="s">
+        <v>56</v>
+      </c>
+      <c r="T56" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C57" s="4"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
+      <c r="A57" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="2">
+        <v>46269</v>
+      </c>
+      <c r="D57" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F57" s="6">
+        <v>67.5792</v>
+      </c>
+      <c r="G57" s="6">
+        <v>15.7844</v>
+      </c>
+      <c r="H57" s="7">
+        <v>67.5792</v>
+      </c>
+      <c r="I57" s="6">
+        <v>15.7844</v>
+      </c>
+      <c r="J57" s="6">
+        <v>2</v>
+      </c>
+      <c r="K57" s="6">
+        <v>10</v>
+      </c>
+      <c r="L57" s="6">
+        <v>50</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>38</v>
+      </c>
+      <c r="R57" t="s">
+        <v>48</v>
+      </c>
+      <c r="T57" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C58" s="4"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
+      <c r="A58" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="2">
+        <v>46269</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="F58" s="6">
+        <v>67.572000000000003</v>
+      </c>
+      <c r="G58" s="6">
+        <v>15.7935</v>
+      </c>
+      <c r="H58" s="6">
+        <v>67.572000000000003</v>
+      </c>
+      <c r="I58" s="6">
+        <v>15.7935</v>
+      </c>
+      <c r="J58" s="6">
+        <v>2</v>
+      </c>
+      <c r="K58" s="6">
+        <v>100</v>
+      </c>
+      <c r="L58" s="6">
+        <v>150</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>38</v>
+      </c>
+      <c r="R58" t="s">
+        <v>48</v>
+      </c>
+      <c r="T58" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C59" s="4"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2">
+        <v>46270</v>
+      </c>
+      <c r="D59" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F59" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="G59" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="H59" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="I59" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="J59" s="6">
+        <v>5</v>
+      </c>
+      <c r="K59" s="6">
+        <v>30</v>
+      </c>
+      <c r="L59" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>38</v>
+      </c>
+      <c r="R59" t="s">
+        <v>48</v>
+      </c>
+      <c r="S59" t="s">
+        <v>122</v>
+      </c>
+      <c r="T59" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C60" s="4"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
+      <c r="A60" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" s="2">
+        <v>46270</v>
+      </c>
+      <c r="D60" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="F60" s="6">
+        <v>67.504000000000005</v>
+      </c>
+      <c r="G60" s="6">
+        <v>15.321400000000001</v>
+      </c>
+      <c r="H60" s="6">
+        <v>67.504000000000005</v>
+      </c>
+      <c r="I60" s="6">
+        <v>15.321400000000001</v>
+      </c>
+      <c r="J60" s="6">
+        <v>5</v>
+      </c>
+      <c r="K60" s="6">
+        <v>50</v>
+      </c>
+      <c r="L60" s="6">
+        <v>150</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>38</v>
+      </c>
+      <c r="R60" t="s">
+        <v>48</v>
+      </c>
+      <c r="T60" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C61" s="4"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
+      <c r="A61" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2">
+        <v>46271</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="F61" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="G61" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="H61" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="I61" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="J61" s="6">
+        <v>5</v>
+      </c>
+      <c r="K61" s="6">
+        <v>30</v>
+      </c>
+      <c r="L61" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>38</v>
+      </c>
+      <c r="R61" t="s">
+        <v>48</v>
+      </c>
+      <c r="S61" t="s">
+        <v>122</v>
+      </c>
+      <c r="T61" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C62" s="4"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
+      <c r="A62" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2">
+        <v>46271</v>
+      </c>
+      <c r="D62" s="3">
+        <v>0.54374999999999996</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0.56319444444444444</v>
+      </c>
+      <c r="F62" s="6">
+        <v>67.516000000000005</v>
+      </c>
+      <c r="G62" s="6">
+        <v>15.481199999999999</v>
+      </c>
+      <c r="H62" s="6">
+        <v>67.516000000000005</v>
+      </c>
+      <c r="I62" s="6">
+        <v>15.481199999999999</v>
+      </c>
+      <c r="J62" s="6">
+        <v>4</v>
+      </c>
+      <c r="K62" s="6">
+        <v>15</v>
+      </c>
+      <c r="L62" s="6">
+        <v>50</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>38</v>
+      </c>
+      <c r="R62" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C63" s="4"/>
